--- a/dataset/construct/dataset_splits/data_size/20_percent/merged/fold1.xlsx
+++ b/dataset/construct/dataset_splits/data_size/20_percent/merged/fold1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AK37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2131</v>
+        <v>1550</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,77 +625,79 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>91.6978407420083</v>
+        <v>84.8388366986083</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>30.4866850321395</v>
       </c>
       <c r="E2" t="n">
-        <v>24.0569347455645</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>110.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>49</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>297.5</v>
+        <v>236</v>
       </c>
       <c r="L2" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>575.2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1238.7</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>86.8</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>93.3</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>110.9</v>
+        <v>23</v>
       </c>
       <c r="V2" t="n">
-        <v>110.9</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>23.332060096766</v>
       </c>
       <c r="X2" t="n">
-        <v>24.9</v>
+        <v>22.7605444857119</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.246478873239437</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.7644512350395</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>24.2811760572589</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -728,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -737,22 +724,13 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
         <v>120</v>
       </c>
-      <c r="AN2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>619</v>
+        <v>899</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -760,82 +738,82 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>74.8920669505919</v>
+        <v>80.2974793076787</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>27.7769298861451</v>
       </c>
       <c r="E3" t="n">
-        <v>24.8015873015873</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>407</v>
       </c>
       <c r="I3" t="n">
-        <v>498</v>
+        <v>208</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>304</v>
       </c>
       <c r="K3" t="n">
-        <v>374</v>
+        <v>919</v>
       </c>
       <c r="L3" t="n">
-        <v>217</v>
+        <v>62</v>
       </c>
       <c r="M3" t="n">
-        <v>148</v>
+        <v>34</v>
       </c>
       <c r="N3" t="n">
-        <v>739</v>
+        <v>155</v>
       </c>
       <c r="O3" t="n">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>8</v>
       </c>
-      <c r="R3" t="n">
-        <v>82</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>27.05</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>27.6928953399542</v>
       </c>
       <c r="X3" t="n">
-        <v>24.4</v>
+        <v>26.9117274486368</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.199261992619926</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>25.0509294626942</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.6608768976369</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -844,39 +822,30 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>693</v>
+        <v>364</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -884,79 +853,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77.651817628717</v>
+        <v>83.7306500177453</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>27.639801313892</v>
       </c>
       <c r="E4" t="n">
-        <v>19.6623076682999</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="I4" t="n">
-        <v>1330</v>
+        <v>72</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>709</v>
+        <v>289</v>
       </c>
       <c r="L4" t="n">
-        <v>417</v>
+        <v>116</v>
       </c>
       <c r="M4" t="n">
-        <v>447</v>
+        <v>16</v>
       </c>
       <c r="N4" t="n">
-        <v>1573</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="P4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>193</v>
+        <v>21.15</v>
       </c>
       <c r="V4" t="n">
-        <v>242</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>21.3267125031831</v>
       </c>
       <c r="X4" t="n">
-        <v>25.1</v>
+        <v>20.8029488434442</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.304054054054054</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>25.7830404889228</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.8203626912254</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -974,31 +943,22 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>368</v>
+        <v>528</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1006,77 +966,79 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.1969855755824</v>
+        <v>84.2009601490608</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>20.5498866213151</v>
       </c>
       <c r="E5" t="n">
-        <v>26.0261748958953</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>118.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>74.2</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1100</v>
+        <v>275</v>
       </c>
       <c r="L5" t="n">
-        <v>297</v>
+        <v>35.2</v>
       </c>
       <c r="M5" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1657</v>
+        <v>6.5</v>
       </c>
       <c r="O5" t="n">
-        <v>33</v>
+        <v>41.7</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>60</v>
+        <v>13.8</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>22.8545963840081</v>
       </c>
       <c r="X5" t="n">
-        <v>22.35</v>
+        <v>22.0850401322991</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.226190476190476</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.9182582123759</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.3940969210825</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1091,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1103,24 +1065,15 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>124</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2308</v>
+        <v>1587</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1128,82 +1081,82 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>76.85541314928891</v>
+        <v>83.3414449768043</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>24.8970602317341</v>
       </c>
       <c r="E6" t="n">
-        <v>28.2828282828282</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>307.5</v>
       </c>
       <c r="I6" t="n">
-        <v>315</v>
+        <v>269.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>185.9</v>
       </c>
       <c r="K6" t="n">
-        <v>387.4</v>
+        <v>762.6</v>
       </c>
       <c r="L6" t="n">
-        <v>356.4</v>
+        <v>8.4</v>
       </c>
       <c r="M6" t="n">
-        <v>395.4</v>
+        <v>42.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1139.2</v>
+        <v>94.8</v>
       </c>
       <c r="O6" t="n">
-        <v>119.7</v>
+        <v>145.7</v>
       </c>
       <c r="P6" t="n">
-        <v>53.2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>175.5</v>
+        <v>18</v>
       </c>
       <c r="R6" t="n">
-        <v>348.4</v>
+        <v>78.8</v>
       </c>
       <c r="S6" t="n">
-        <v>14.9</v>
+        <v>96.8</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>127.4</v>
+        <v>23.15</v>
       </c>
       <c r="V6" t="n">
-        <v>142.3</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X6" t="n">
-        <v>23.05</v>
+        <v>23.0936433298824</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.298892988929889</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.8545963840081</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.1741916431478</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1227,24 +1180,15 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>256</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1315</v>
+        <v>2413</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1252,85 +1196,85 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>77.34847025756081</v>
+        <v>83.4834113494055</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>37.6542220797949</v>
       </c>
       <c r="E7" t="n">
-        <v>29.0687732977668</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>1003.9</v>
       </c>
       <c r="I7" t="n">
-        <v>933</v>
+        <v>83</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>22.2</v>
       </c>
       <c r="K7" t="n">
-        <v>645.9</v>
+        <v>1109.1</v>
       </c>
       <c r="L7" t="n">
-        <v>346.9</v>
+        <v>34.4</v>
       </c>
       <c r="M7" t="n">
-        <v>419.5</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1412.3</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="P7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>98.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>22.55</v>
       </c>
       <c r="V7" t="n">
-        <v>26</v>
+        <v>0.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>23.1729055258467</v>
       </c>
       <c r="X7" t="n">
-        <v>26.8</v>
+        <v>22.6034185328367</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.207357859531773</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>27.6292335115865</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>26.9920118011893</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1345,30 +1289,21 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2338</v>
+        <v>1720</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1376,121 +1311,114 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>89.2657497718458</v>
+        <v>68.3052995474941</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>30.7173999207292</v>
       </c>
       <c r="E8" t="n">
-        <v>25.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>166.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>262</v>
+      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>248</v>
       </c>
       <c r="K8" t="n">
-        <v>237.9</v>
+        <v>676.7</v>
       </c>
       <c r="L8" t="n">
-        <v>111.4</v>
+        <v>44.4</v>
       </c>
       <c r="M8" t="n">
-        <v>42.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>391.7</v>
+        <v>95.2</v>
       </c>
       <c r="O8" t="n">
-        <v>72.8</v>
+        <v>139.6</v>
       </c>
       <c r="P8" t="n">
-        <v>5.7</v>
+        <v>23.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>102.5</v>
+        <v>99.8</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>123.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>46.5</v>
+        <v>24.25</v>
       </c>
       <c r="V8" t="n">
-        <v>46.5</v>
+        <v>0.29</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X8" t="n">
-        <v>19.65</v>
+        <v>23.0936433298824</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.205479452054795</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.9261522790935</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.6934438757455</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>220</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>471</v>
+        <v>556</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1498,79 +1426,79 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>75.0402101553984</v>
+        <v>78.32835766978479</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>25.8264462809917</v>
       </c>
       <c r="E9" t="n">
-        <v>24.2105958514995</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>55</v>
+        <v>855</v>
       </c>
       <c r="I9" t="n">
-        <v>200</v>
+        <v>523</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>457</v>
       </c>
       <c r="K9" t="n">
-        <v>464</v>
+        <v>1835</v>
       </c>
       <c r="L9" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1824</v>
+        <v>77</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>24.95</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>26.1013496307614</v>
       </c>
       <c r="X9" t="n">
-        <v>25.8</v>
+        <v>24.9992044677091</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>25.6557168321874</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>24.7175864208069</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1579,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1588,33 +1516,24 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1622,77 +1541,79 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>85.91221886328491</v>
+        <v>82.3836315499278</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>29.585798816568</v>
       </c>
       <c r="E10" t="n">
-        <v>25.8805706350208</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>45</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>291</v>
+      </c>
+      <c r="I10" t="n">
+        <v>121</v>
+      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="K10" t="n">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="L10" t="n">
-        <v>378</v>
+        <v>50</v>
       </c>
       <c r="M10" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1013</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>52</v>
       </c>
       <c r="P10" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>21.4</v>
       </c>
       <c r="V10" t="n">
-        <v>33</v>
+        <v>0.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>21.6450216450216</v>
       </c>
       <c r="X10" t="n">
-        <v>29.3</v>
+        <v>20.9857015385198</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.16875</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>28.9661319073084</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>28.6082260699118</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1719,24 +1640,15 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>254</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>657</v>
+        <v>914</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1744,82 +1656,82 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83.0759392349228</v>
+        <v>84.0671732958146</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>25.7629805786761</v>
       </c>
       <c r="E11" t="n">
-        <v>28.6501377410468</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
+        <v>855</v>
+      </c>
+      <c r="I11" t="n">
+        <v>534</v>
+      </c>
+      <c r="J11" t="n">
+        <v>428</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1817</v>
+      </c>
+      <c r="L11" t="n">
         <v>50</v>
       </c>
-      <c r="I11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>819.2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>99.09999999999999</v>
-      </c>
       <c r="M11" t="n">
-        <v>237.1</v>
+        <v>7</v>
       </c>
       <c r="N11" t="n">
-        <v>1155.4</v>
+        <v>113</v>
       </c>
       <c r="O11" t="n">
-        <v>19.5</v>
+        <v>170</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>40.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>59.7</v>
+        <v>93</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>29.921059332824</v>
       </c>
       <c r="X11" t="n">
-        <v>21.85</v>
+        <v>29.2679951700071</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.357142857142857</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.3002291825821</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>22.1454723050462</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1828,37 +1740,28 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="n">
-        <v>200</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>54731805</v>
+        <v>52759086</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1866,74 +1769,88 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>79.0225872689938</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>70.8692676249144</v>
+      </c>
+      <c r="D12" t="n">
+        <v>26.7949380165289</v>
+      </c>
       <c r="E12" t="n">
-        <v>28.7211210705719</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>55</v>
+      </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>130</v>
+      </c>
+      <c r="I12" t="n">
+        <v>135</v>
+      </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+        <v>117</v>
+      </c>
+      <c r="K12" t="n">
+        <v>382</v>
+      </c>
+      <c r="L12" t="n">
+        <v>130</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87</v>
+      </c>
+      <c r="N12" t="n">
+        <v>117</v>
+      </c>
       <c r="O12" t="n">
-        <v>730</v>
+        <v>334</v>
       </c>
       <c r="P12" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>860</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>25.14648100851947</v>
       </c>
       <c r="X12" t="n">
-        <v>24.7</v>
+        <v>24.69578388972788</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>78.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>471</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,33 +1859,24 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>173</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>54048115</v>
+        <v>53110975</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1976,67 +1884,79 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>91.61122518822719</v>
+        <v>86.1437371663244</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>24.2214532871972</v>
       </c>
       <c r="E13" t="n">
-        <v>25.7116620752984</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>55</v>
+      </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>50</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>458</v>
+      </c>
+      <c r="I13" t="n">
+        <v>173</v>
+      </c>
       <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+        <v>86</v>
+      </c>
+      <c r="K13" t="n">
+        <v>717</v>
+      </c>
+      <c r="L13" t="n">
+        <v>437</v>
+      </c>
+      <c r="M13" t="n">
+        <v>173</v>
+      </c>
+      <c r="N13" t="n">
+        <v>86</v>
+      </c>
       <c r="O13" t="n">
-        <v>29</v>
+        <v>696</v>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>222</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>25.1</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>25.71943880365029</v>
       </c>
       <c r="X13" t="n">
-        <v>20.9</v>
+        <v>24.71897363400035</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>66.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>332.7</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2051,36 +1971,27 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>181</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>54131344</v>
+        <v>54322069</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2088,79 +1999,83 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>76.3750855578371</v>
+        <v>82.3791923340178</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>25.6172839506173</v>
       </c>
       <c r="E14" t="n">
-        <v>30.7173999207293</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>41</v>
+      </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>56</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>105</v>
+      </c>
+      <c r="M14" t="n">
+        <v>214</v>
+      </c>
+      <c r="N14" t="n">
+        <v>155</v>
+      </c>
       <c r="O14" t="n">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="P14" t="n">
-        <v>674</v>
+        <v>25</v>
       </c>
       <c r="Q14" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1267</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>27.34281922318762</v>
       </c>
       <c r="X14" t="n">
-        <v>25.9</v>
+        <v>26.53730943771464</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>539.3</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2175,24 +2090,15 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>168</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>214</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>51921494</v>
+        <v>54990570</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2200,86 +2106,80 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>85.06502395619439</v>
+        <v>77.5797399041752</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>41.3223140495868</v>
       </c>
       <c r="E15" t="n">
-        <v>23.3843537414966</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>45</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>649</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>377</v>
+        <v>275</v>
       </c>
       <c r="M15" t="n">
-        <v>684</v>
+        <v>153</v>
       </c>
       <c r="N15" t="n">
-        <v>1710</v>
+        <v>260</v>
       </c>
       <c r="O15" t="n">
-        <v>609</v>
+        <v>688</v>
       </c>
       <c r="P15" t="n">
-        <v>274</v>
+        <v>115</v>
       </c>
       <c r="Q15" t="n">
-        <v>618</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1501</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>24</v>
+        <v>115</v>
       </c>
       <c r="T15" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V15" t="n">
-        <v>76</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>28.36141085897575</v>
       </c>
       <c r="X15" t="n">
-        <v>27.4</v>
+        <v>25.19344980447256</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>89.7</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>609.6</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2288,29 +2188,20 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>53103442</v>
+        <v>52104722</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2318,73 +2209,85 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>72.4955509924709</v>
+        <v>81.11430527036281</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>27.5873260578522</v>
       </c>
       <c r="E16" t="n">
-        <v>25.9701155481953</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>55</v>
+      </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
+        <v>27</v>
+      </c>
+      <c r="I16" t="n">
+        <v>18</v>
+      </c>
+      <c r="J16" t="n">
         <v>55</v>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>100</v>
+      </c>
+      <c r="L16" t="n">
+        <v>27</v>
+      </c>
+      <c r="M16" t="n">
+        <v>18</v>
+      </c>
+      <c r="N16" t="n">
+        <v>55</v>
+      </c>
       <c r="O16" t="n">
-        <v>104.85053</v>
+        <v>100</v>
       </c>
       <c r="P16" t="n">
-        <v>14.369488</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.0514259</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>120.271454</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>27.47014317766114</v>
       </c>
       <c r="X16" t="n">
-        <v>23.045048</v>
+        <v>26.53011157778267</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>72.54245</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>398.6611</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2396,29 +2299,24 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
+        <v>162</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>54107625</v>
+        <v>54405222</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2426,67 +2324,71 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>78.15742642026009</v>
+        <v>83.2717316906229</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>22.4323025156225</v>
       </c>
       <c r="E17" t="n">
-        <v>23.7953599048186</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>49</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="n">
-        <v>63</v>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>84</v>
+      </c>
+      <c r="M17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>31</v>
+      </c>
       <c r="O17" t="n">
-        <v>542</v>
+        <v>123</v>
       </c>
       <c r="P17" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1070</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>292</v>
+        <v>23</v>
       </c>
       <c r="V17" t="n">
-        <v>312</v>
+        <v>0.22</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>23.39577663450861</v>
       </c>
       <c r="X17" t="n">
-        <v>24.4</v>
+        <v>23.03939161957384</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>78.2</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>464.4</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2504,33 +2406,24 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>53030162</v>
+        <v>54615005</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2538,87 +2431,83 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>84.0848733744011</v>
+        <v>81.1033538672142</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>27.1604938271605</v>
       </c>
       <c r="E18" t="n">
-        <v>42.0395421436004</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>55</v>
+      </c>
       <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>287</v>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>180</v>
+        <v>819</v>
       </c>
       <c r="M18" t="n">
-        <v>143</v>
+        <v>446</v>
       </c>
       <c r="N18" t="n">
-        <v>610</v>
+        <v>437</v>
       </c>
       <c r="O18" t="n">
-        <v>287</v>
+        <v>1702</v>
       </c>
       <c r="P18" t="n">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="R18" t="n">
-        <v>567</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>27.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>27.27915724595086</v>
       </c>
       <c r="X18" t="n">
-        <v>22.9</v>
+        <v>27.03168834393275</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>378.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2627,30 +2516,21 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>186</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>156</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>52535955</v>
+        <v>52832940</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2658,117 +2538,114 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>92.6351813826146</v>
+        <v>76.7556468172485</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>23.5102040816327</v>
       </c>
       <c r="E19" t="n">
-        <v>19.53125</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>37</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>561</v>
+      </c>
+      <c r="I19" t="n">
+        <v>813</v>
+      </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="K19" t="n">
-        <v>134</v>
+        <v>1834</v>
       </c>
       <c r="L19" t="n">
-        <v>81</v>
+        <v>540</v>
       </c>
       <c r="M19" t="n">
-        <v>84</v>
+        <v>495</v>
       </c>
       <c r="N19" t="n">
-        <v>299</v>
+        <v>433</v>
       </c>
       <c r="O19" t="n">
-        <v>134</v>
+        <v>1468</v>
       </c>
       <c r="P19" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="R19" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>372</v>
+        <v>28.1</v>
       </c>
       <c r="V19" t="n">
-        <v>377</v>
+        <v>0.25</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>28.52056580206764</v>
       </c>
       <c r="X19" t="n">
-        <v>23.1</v>
+        <v>27.74298658746758</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>75.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>427.8</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
+        <v>148</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>55774208</v>
+        <v>51434872</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2776,71 +2653,83 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>90.2094455852156</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>78.3490759753593</v>
+      </c>
+      <c r="D20" t="n">
+        <v>26.3365484599663</v>
+      </c>
       <c r="E20" t="n">
-        <v>27.3981756824485</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>56</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>388</v>
+      </c>
+      <c r="I20" t="n">
+        <v>654</v>
+      </c>
       <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>280</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1322</v>
+      </c>
+      <c r="L20" t="n">
+        <v>370</v>
+      </c>
+      <c r="M20" t="n">
+        <v>232</v>
+      </c>
+      <c r="N20" t="n">
+        <v>237</v>
+      </c>
       <c r="O20" t="n">
-        <v>504.98007</v>
+        <v>839</v>
       </c>
       <c r="P20" t="n">
-        <v>338.65198</v>
+        <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>507.86694</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1351.499</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>30</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="V20" t="n">
-        <v>30</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>25.30563595161136</v>
       </c>
       <c r="X20" t="n">
-        <v>26.27235</v>
+        <v>24.74471452781664</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>81.84308</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>505.84912</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -2849,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
         <v>0</v>
@@ -2861,24 +2750,15 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>144</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>51208627</v>
+        <v>51838049</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2886,80 +2766,82 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>80.0027378507871</v>
+        <v>78.7132101300479</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>21.0480476121353</v>
       </c>
       <c r="E21" t="n">
-        <v>22.1453287197232</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
+        <v>212</v>
+      </c>
+      <c r="I21" t="n">
+        <v>130</v>
+      </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>670</v>
+        <v>356</v>
       </c>
       <c r="L21" t="n">
-        <v>866</v>
+        <v>212</v>
       </c>
       <c r="M21" t="n">
-        <v>922</v>
+        <v>86</v>
       </c>
       <c r="N21" t="n">
-        <v>2459</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
-        <v>670</v>
+        <v>312</v>
       </c>
       <c r="P21" t="n">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1974</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>26.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>27.34281922318762</v>
       </c>
       <c r="X21" t="n">
-        <v>30.5</v>
+        <v>26.27209845446176</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>98.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>748.6</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -2971,32 +2853,27 @@
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
+        <v>120</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>55005074</v>
+        <v>52017566</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3004,74 +2881,88 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>90.03422313483919</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>78.19849418206709</v>
+      </c>
+      <c r="D22" t="n">
+        <v>40.0367309458219</v>
+      </c>
       <c r="E22" t="n">
-        <v>28.125</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>45</v>
+      </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>55</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>546</v>
+      </c>
+      <c r="I22" t="n">
+        <v>696</v>
+      </c>
       <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1569</v>
+      </c>
+      <c r="L22" t="n">
+        <v>321</v>
+      </c>
+      <c r="M22" t="n">
+        <v>338</v>
+      </c>
+      <c r="N22" t="n">
+        <v>239</v>
+      </c>
       <c r="O22" t="n">
-        <v>177</v>
+        <v>898</v>
       </c>
       <c r="P22" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>417</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>26.22873462154435</v>
       </c>
       <c r="X22" t="n">
-        <v>22</v>
+        <v>25.76314760797757</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>367.8</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3083,30 +2974,17 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>144</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>135</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>53842501</v>
+        <v>52884841</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3114,74 +2992,88 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>84.0273785078713</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+        <v>86.4777549623546</v>
+      </c>
+      <c r="D23" t="n">
+        <v>28.4005479635136</v>
+      </c>
       <c r="E23" t="n">
-        <v>22.2753099173554</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>45</v>
+      </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>45</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>462</v>
+      </c>
+      <c r="I23" t="n">
+        <v>223</v>
+      </c>
       <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+        <v>355</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1040</v>
+      </c>
+      <c r="L23" t="n">
+        <v>397</v>
+      </c>
+      <c r="M23" t="n">
+        <v>207</v>
+      </c>
+      <c r="N23" t="n">
+        <v>355</v>
+      </c>
       <c r="O23" t="n">
-        <v>180</v>
+        <v>959</v>
       </c>
       <c r="P23" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>630</v>
+        <v>60</v>
       </c>
       <c r="S23" t="n">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>51</v>
+        <v>27.8</v>
       </c>
       <c r="V23" t="n">
-        <v>167</v>
+        <v>0.19</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>29.18901656305361</v>
       </c>
       <c r="X23" t="n">
-        <v>25.2</v>
+        <v>28.17560746714033</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>79.2</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>479.8</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3190,33 +3082,24 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="AK23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>152</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>51434913</v>
+        <v>53475944</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3224,63 +3107,79 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>84.6762491444216</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
+        <v>83.8904859685147</v>
+      </c>
+      <c r="D24" t="n">
+        <v>20.1732526403228</v>
+      </c>
       <c r="E24" t="n">
-        <v>29.296875</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>55</v>
+      </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>102</v>
+      </c>
+      <c r="I24" t="n">
+        <v>88</v>
+      </c>
       <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="K24" t="n">
+        <v>257</v>
+      </c>
+      <c r="L24" t="n">
+        <v>966</v>
+      </c>
+      <c r="M24" t="n">
+        <v>66</v>
+      </c>
+      <c r="N24" t="n">
+        <v>38</v>
+      </c>
       <c r="O24" t="n">
-        <v>812.4044</v>
+        <v>1070</v>
       </c>
       <c r="P24" t="n">
-        <v>318.00055</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>233.35861</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1363.7635</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W24" t="n">
-        <v>2</v>
+        <v>19.67155096615826</v>
       </c>
       <c r="X24" t="n">
-        <v>28.752941</v>
+        <v>19.12594366828503</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>91.23679</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>637.6867999999999</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3301,30 +3200,21 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>192</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>53762758</v>
+        <v>53204255</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3332,117 +3222,110 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>69.8151950718686</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>77.63449691991789</v>
+      </c>
+      <c r="D25" t="n">
+        <v>23.4509182190514</v>
+      </c>
       <c r="E25" t="n">
-        <v>27.0416441319632</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>55</v>
+      </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>55</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>550</v>
+      </c>
+      <c r="I25" t="n">
+        <v>554</v>
+      </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>453</v>
       </c>
       <c r="K25" t="n">
-        <v>131</v>
+        <v>1557</v>
       </c>
       <c r="L25" t="n">
-        <v>135</v>
+        <v>550</v>
       </c>
       <c r="M25" t="n">
-        <v>63</v>
+        <v>554</v>
       </c>
       <c r="N25" t="n">
-        <v>329</v>
+        <v>446</v>
       </c>
       <c r="O25" t="n">
-        <v>57</v>
+        <v>1550</v>
       </c>
       <c r="P25" t="n">
-        <v>130</v>
+        <v>7</v>
       </c>
       <c r="Q25" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>250</v>
+        <v>298</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>26.80169241667518</v>
       </c>
       <c r="X25" t="n">
-        <v>25</v>
+        <v>26.10924074444154</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>478.4</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
       </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>129</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>168</v>
-      </c>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>51664457</v>
+        <v>54177281</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3450,86 +3333,80 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>86.1738535249829</v>
+        <v>80.4517453798768</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>35.323147647377</v>
       </c>
       <c r="E26" t="n">
-        <v>19.687825182102</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="n">
-        <v>55</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>407</v>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>59</v>
+        <v>385</v>
       </c>
       <c r="M26" t="n">
-        <v>201</v>
+        <v>91</v>
       </c>
       <c r="N26" t="n">
-        <v>667</v>
+        <v>95</v>
       </c>
       <c r="O26" t="n">
-        <v>401</v>
+        <v>571</v>
       </c>
       <c r="P26" t="n">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="Q26" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>609</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>24.2</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>25.87859374674218</v>
       </c>
       <c r="X26" t="n">
-        <v>29.9</v>
+        <v>24.27458055875391</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>99.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>693.4</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3541,30 +3418,21 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>198</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>190</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>52884154</v>
+        <v>52076751</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3572,73 +3440,47 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>89.7796030116359</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
+        <v>87.33196440793979</v>
+      </c>
+      <c r="D27" t="n">
+        <v>29.4321329639889</v>
+      </c>
       <c r="E27" t="n">
-        <v>23.191094619666</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>60</v>
+      </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>481</v>
-      </c>
-      <c r="L27" t="n">
-        <v>927</v>
-      </c>
-      <c r="M27" t="n">
-        <v>548</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1956</v>
-      </c>
-      <c r="O27" t="n">
-        <v>472</v>
-      </c>
-      <c r="P27" t="n">
-        <v>656</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>519</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1647</v>
-      </c>
-      <c r="S27" t="n">
-        <v>140</v>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>10</v>
-      </c>
-      <c r="U27" t="n">
-        <v>297</v>
-      </c>
-      <c r="V27" t="n">
-        <v>448</v>
-      </c>
-      <c r="W27" t="n">
         <v>2</v>
       </c>
-      <c r="X27" t="n">
-        <v>25.9</v>
-      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
-        <v>0.22</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>83.5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>519.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3653,32 +3495,27 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="AK27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
+        <v>142</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>52715972</v>
+        <v>51890467</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3686,73 +3523,77 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>75.8713210130048</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+        <v>87.57837097878171</v>
+      </c>
+      <c r="D28" t="n">
+        <v>32.0105109140315</v>
+      </c>
       <c r="E28" t="n">
-        <v>26.0145681581686</v>
+        <v>1</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>61</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
+        <v>566</v>
+      </c>
+      <c r="I28" t="n">
+        <v>830</v>
+      </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>532</v>
       </c>
       <c r="K28" t="n">
-        <v>1305</v>
+        <v>1928</v>
       </c>
       <c r="L28" t="n">
-        <v>778</v>
+        <v>566</v>
       </c>
       <c r="M28" t="n">
-        <v>474</v>
+        <v>350</v>
       </c>
       <c r="N28" t="n">
-        <v>2556</v>
+        <v>519</v>
       </c>
       <c r="O28" t="n">
-        <v>1305</v>
+        <v>1435</v>
       </c>
       <c r="P28" t="n">
-        <v>778</v>
+        <v>68</v>
       </c>
       <c r="Q28" t="n">
-        <v>474</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2556</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>421</v>
+        <v>68</v>
       </c>
       <c r="T28" t="n">
-        <v>399</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>480</v>
+        <v>31</v>
       </c>
       <c r="V28" t="n">
-        <v>1300</v>
+        <v>0.2</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>30.65324203949904</v>
       </c>
       <c r="X28" t="n">
-        <v>29</v>
+        <v>30.24182476278948</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="n">
-        <v>90.8</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>635.9</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3764,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -3779,24 +3620,15 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>201</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>53802342</v>
+        <v>51286310</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3804,74 +3636,88 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>82.3846680355921</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
+        <v>78.258726899384</v>
+      </c>
+      <c r="D29" t="n">
+        <v>33.2179930795848</v>
+      </c>
       <c r="E29" t="n">
-        <v>27.170631566236</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>55</v>
+      </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>55</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>268</v>
+      </c>
+      <c r="I29" t="n">
+        <v>374</v>
+      </c>
       <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+        <v>285</v>
+      </c>
+      <c r="K29" t="n">
+        <v>927</v>
+      </c>
+      <c r="L29" t="n">
+        <v>191</v>
+      </c>
+      <c r="M29" t="n">
+        <v>322</v>
+      </c>
+      <c r="N29" t="n">
+        <v>238</v>
+      </c>
       <c r="O29" t="n">
-        <v>201</v>
+        <v>751</v>
       </c>
       <c r="P29" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="V29" t="n">
-        <v>230</v>
+        <v>0.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>26.64253747358328</v>
       </c>
       <c r="X29" t="n">
-        <v>28.8</v>
+        <v>26.05554308113321</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>92.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>636.1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3889,20 +3735,15 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="AK29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
+        <v>102</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>55008748</v>
+        <v>55818337</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3910,71 +3751,77 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>82.8692676249144</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
+        <v>83.7070499657769</v>
+      </c>
+      <c r="D30" t="n">
+        <v>28.3675236644868</v>
+      </c>
       <c r="E30" t="n">
-        <v>24.2512783053324</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>42</v>
+      </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>127.83168</v>
+      </c>
+      <c r="M30" t="n">
+        <v>267.0387</v>
+      </c>
+      <c r="N30" t="n">
+        <v>151.37073</v>
+      </c>
       <c r="O30" t="n">
-        <v>432</v>
+        <v>546.24111</v>
       </c>
       <c r="P30" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1127</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>97</v>
+        <v>25.884556</v>
       </c>
       <c r="V30" t="n">
-        <v>188</v>
+        <v>0.26</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>26.31333947943269</v>
       </c>
       <c r="X30" t="n">
-        <v>25.5</v>
+        <v>25.8501732722776</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>82.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -3983,10 +3830,10 @@
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
         <v>0</v>
@@ -3995,24 +3842,15 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>194</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>52987727</v>
+        <v>51368301</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4020,73 +3858,79 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>88.67077344284741</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
+        <v>77.4893908281999</v>
+      </c>
+      <c r="D31" t="n">
+        <v>18.4672206832872</v>
+      </c>
       <c r="E31" t="n">
-        <v>22.4323025156225</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>23</v>
+      </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>55</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
+        <v>394</v>
+      </c>
+      <c r="I31" t="n">
+        <v>261</v>
+      </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>398</v>
       </c>
       <c r="K31" t="n">
-        <v>315</v>
+        <v>1053</v>
       </c>
       <c r="L31" t="n">
-        <v>181</v>
+        <v>360</v>
       </c>
       <c r="M31" t="n">
-        <v>123</v>
+        <v>252</v>
       </c>
       <c r="N31" t="n">
-        <v>619</v>
+        <v>351</v>
       </c>
       <c r="O31" t="n">
-        <v>315</v>
+        <v>963</v>
       </c>
       <c r="P31" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>587</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>14</v>
+        <v>29.4</v>
       </c>
       <c r="V31" t="n">
-        <v>14</v>
+        <v>0.23</v>
       </c>
       <c r="W31" t="n">
-        <v>2</v>
+        <v>29.41183348338226</v>
       </c>
       <c r="X31" t="n">
-        <v>23.2</v>
+        <v>28.9050132201183</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>73.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA31" t="n">
-        <v>411.5</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -4095,38 +3939,29 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
       </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>54710298</v>
+        <v>54535871</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4134,109 +3969,106 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>74.1902806297057</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
+        <v>75.41409993155369</v>
+      </c>
+      <c r="D32" t="n">
+        <v>32.8719723183391</v>
+      </c>
       <c r="E32" t="n">
-        <v>31.3145661157025</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>53</v>
+      </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="n">
-        <v>55</v>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>234</v>
+      </c>
+      <c r="M32" t="n">
+        <v>131</v>
+      </c>
+      <c r="N32" t="n">
+        <v>282</v>
+      </c>
       <c r="O32" t="n">
-        <v>326</v>
+        <v>647</v>
       </c>
       <c r="P32" t="n">
-        <v>252</v>
+        <v>16</v>
       </c>
       <c r="Q32" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>806</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>25.1</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>0.21</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>25.84676275812381</v>
       </c>
       <c r="X32" t="n">
-        <v>25.9</v>
+        <v>25.09216919422348</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>84.5</v>
+        <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>526.6</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>124</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>54615339</v>
+        <v>51903886</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4244,71 +4076,85 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>85.39356605065019</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
+        <v>81.96303901437371</v>
+      </c>
+      <c r="D33" t="n">
+        <v>24.8015873015873</v>
+      </c>
       <c r="E33" t="n">
-        <v>24.2512783053324</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>60</v>
+      </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>50</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
+        <v>216</v>
+      </c>
+      <c r="I33" t="n">
+        <v>58</v>
+      </c>
       <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+        <v>129</v>
+      </c>
+      <c r="K33" t="n">
+        <v>403</v>
+      </c>
+      <c r="L33" t="n">
+        <v>216</v>
+      </c>
+      <c r="M33" t="n">
+        <v>23</v>
+      </c>
+      <c r="N33" t="n">
+        <v>110</v>
+      </c>
       <c r="O33" t="n">
-        <v>232</v>
+        <v>349</v>
       </c>
       <c r="P33" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>418</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>27.2</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>28.20225591588385</v>
       </c>
       <c r="X33" t="n">
-        <v>26.8</v>
+        <v>26.87580312713013</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>84.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>561.2</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4317,36 +4163,23 @@
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
       </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>228</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>143</v>
-      </c>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>54786923</v>
+        <v>53810519</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4354,68 +4187,74 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>74.4284736481862</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
+        <v>71.66050650239561</v>
+      </c>
+      <c r="D34" t="n">
+        <v>29.0367377856331</v>
+      </c>
       <c r="E34" t="n">
-        <v>25.013520822066</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>59</v>
+      </c>
       <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>60</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>711</v>
+      </c>
+      <c r="M34" t="n">
+        <v>776</v>
+      </c>
+      <c r="N34" t="n">
+        <v>376</v>
+      </c>
       <c r="O34" t="n">
-        <v>115</v>
+        <v>1863</v>
       </c>
       <c r="P34" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>474</v>
+        <v>23</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>28.8</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>29.63465040371091</v>
       </c>
       <c r="X34" t="n">
-        <v>25.6</v>
+        <v>29.3118072589748</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="Z34" t="n">
-        <v>86.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>535.8</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4424,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4439,24 +4278,15 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="AK34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>118</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>174</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>55371149</v>
+        <v>53465255</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4464,74 +4294,80 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>87.57837097878171</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
+        <v>87.7262149212868</v>
+      </c>
+      <c r="D35" t="n">
+        <v>24.2214532871972</v>
+      </c>
       <c r="E35" t="n">
-        <v>23.8754325259516</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>50</v>
+      </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="n">
-        <v>56</v>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>203.90793</v>
+      </c>
+      <c r="M35" t="n">
+        <v>171.7652</v>
+      </c>
+      <c r="N35" t="n">
+        <v>116.42987</v>
+      </c>
       <c r="O35" t="n">
-        <v>557.88806</v>
+        <v>492.103</v>
       </c>
       <c r="P35" t="n">
-        <v>131.21591</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>165.44266</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>854.5466300000001</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>24.351166</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W35" t="n">
-        <v>2</v>
+        <v>24.51791129317347</v>
       </c>
       <c r="X35" t="n">
-        <v>23.621138</v>
+        <v>24.29145517808263</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>78.52612000000001</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>459.9465</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4540,33 +4376,24 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="AK35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>212</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>51855654</v>
+        <v>52997836</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4574,86 +4401,88 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>72.33949349760439</v>
+        <v>86.48323066392879</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>24.6913580246914</v>
       </c>
       <c r="E36" t="n">
-        <v>31.1418685121107</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>42</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
+        <v>557</v>
+      </c>
+      <c r="I36" t="n">
+        <v>755</v>
+      </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>275</v>
       </c>
       <c r="K36" t="n">
-        <v>370</v>
+        <v>1587</v>
       </c>
       <c r="L36" t="n">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="M36" t="n">
-        <v>203</v>
+        <v>592</v>
       </c>
       <c r="N36" t="n">
-        <v>813</v>
+        <v>266</v>
       </c>
       <c r="O36" t="n">
-        <v>370</v>
+        <v>1106</v>
       </c>
       <c r="P36" t="n">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="Q36" t="n">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="R36" t="n">
-        <v>666</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>28.99803063134333</v>
       </c>
       <c r="X36" t="n">
-        <v>28.8</v>
+        <v>28.08281634752754</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>92.2</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>631.5</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4671,20 +4500,15 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
+        <v>162</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>51198311</v>
+        <v>54638335</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4692,82 +4516,80 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>77.67830253251201</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
+        <v>87.53730321697471</v>
+      </c>
+      <c r="D37" t="n">
+        <v>23.6712536295922</v>
+      </c>
       <c r="E37" t="n">
-        <v>25.3515413737155</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>25</v>
+      </c>
       <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="n">
-        <v>55</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>399</v>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>284</v>
+        <v>101</v>
       </c>
       <c r="M37" t="n">
-        <v>304</v>
+        <v>70</v>
       </c>
       <c r="N37" t="n">
-        <v>987</v>
+        <v>91</v>
       </c>
       <c r="O37" t="n">
-        <v>381</v>
+        <v>262</v>
       </c>
       <c r="P37" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>896</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>239</v>
+        <v>24.6</v>
       </c>
       <c r="V37" t="n">
-        <v>414</v>
+        <v>0.33</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>26.22873462154435</v>
       </c>
       <c r="X37" t="n">
-        <v>27.5</v>
+        <v>25.10231564396863</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>86.3</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>564.7</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -4785,16 +4607,11 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="AK37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
